--- a/data/plejd_trends_monthly.xlsx
+++ b/data/plejd_trends_monthly.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J124"/>
+  <dimension ref="A1:J126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,7 +477,7 @@
         <v>42400</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -669,7 +669,7 @@
         <v>42582</v>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -733,7 +733,7 @@
         <v>42643</v>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -765,7 +765,7 @@
         <v>42674</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -818,7 +818,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -931,7 +931,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
         <v>42916</v>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1181,7 +1181,7 @@
         <v>43069</v>
       </c>
       <c r="B24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
@@ -1341,7 +1341,7 @@
         <v>43220</v>
       </c>
       <c r="B29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -1437,7 +1437,7 @@
         <v>43312</v>
       </c>
       <c r="B32" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
@@ -1533,7 +1533,7 @@
         <v>43404</v>
       </c>
       <c r="B35" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
@@ -1606,7 +1606,7 @@
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -1629,7 +1629,7 @@
         <v>43496</v>
       </c>
       <c r="B38" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -1693,7 +1693,7 @@
         <v>43555</v>
       </c>
       <c r="B40" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
@@ -1711,7 +1711,7 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
@@ -1728,7 +1728,7 @@
         <v>15</v>
       </c>
       <c r="C41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -1792,7 +1792,7 @@
         <v>14</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
@@ -1888,7 +1888,7 @@
         <v>22</v>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
@@ -2019,7 +2019,7 @@
         <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
         <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
@@ -2083,7 +2083,7 @@
         <v>2</v>
       </c>
       <c r="D52" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
@@ -2109,7 +2109,7 @@
         <v>43951</v>
       </c>
       <c r="B53" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C53" t="n">
         <v>2</v>
@@ -2240,7 +2240,7 @@
         <v>24</v>
       </c>
       <c r="C57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D57" t="n">
         <v>0</v>
@@ -2275,7 +2275,7 @@
         <v>3</v>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
@@ -2325,7 +2325,7 @@
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
     </row>
     <row r="60">
@@ -2348,7 +2348,7 @@
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -2371,7 +2371,7 @@
         <v>6</v>
       </c>
       <c r="D61" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="E61" t="n">
         <v>0</v>
@@ -2400,10 +2400,10 @@
         <v>35</v>
       </c>
       <c r="C62" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D62" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E62" t="n">
         <v>0</v>
@@ -2435,7 +2435,7 @@
         <v>8</v>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
@@ -2464,10 +2464,10 @@
         <v>32</v>
       </c>
       <c r="C64" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D64" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
@@ -2499,7 +2499,7 @@
         <v>5</v>
       </c>
       <c r="D65" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E65" t="n">
         <v>0</v>
@@ -2557,7 +2557,7 @@
         <v>44377</v>
       </c>
       <c r="B67" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C67" t="n">
         <v>5</v>
@@ -2589,10 +2589,10 @@
         <v>44408</v>
       </c>
       <c r="B68" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C68" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D68" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
         <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -2621,13 +2621,13 @@
         <v>44439</v>
       </c>
       <c r="B69" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C69" t="n">
         <v>5</v>
       </c>
       <c r="D69" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E69" t="n">
         <v>0</v>
@@ -2653,13 +2653,13 @@
         <v>44469</v>
       </c>
       <c r="B70" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C70" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D70" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E70" t="n">
         <v>0</v>
@@ -2688,7 +2688,7 @@
         <v>39</v>
       </c>
       <c r="C71" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D71" t="n">
         <v>0</v>
@@ -2717,13 +2717,13 @@
         <v>44530</v>
       </c>
       <c r="B72" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C72" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D72" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E72" t="n">
         <v>0</v>
@@ -2781,13 +2781,13 @@
         <v>44592</v>
       </c>
       <c r="B74" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C74" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D74" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="E74" t="n">
         <v>0</v>
@@ -2813,13 +2813,13 @@
         <v>44620</v>
       </c>
       <c r="B75" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C75" t="n">
         <v>12</v>
       </c>
       <c r="D75" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E75" t="n">
         <v>0</v>
@@ -2851,10 +2851,10 @@
         <v>12</v>
       </c>
       <c r="D76" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E76" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
@@ -2880,10 +2880,10 @@
         <v>30</v>
       </c>
       <c r="C77" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D77" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E77" t="n">
         <v>0</v>
@@ -2915,7 +2915,7 @@
         <v>10</v>
       </c>
       <c r="D78" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E78" t="n">
         <v>0</v>
@@ -2941,10 +2941,10 @@
         <v>44742</v>
       </c>
       <c r="B79" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C79" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D79" t="n">
         <v>0</v>
@@ -2976,10 +2976,10 @@
         <v>25</v>
       </c>
       <c r="C80" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D80" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E80" t="n">
         <v>0</v>
@@ -3005,13 +3005,13 @@
         <v>44804</v>
       </c>
       <c r="B81" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C81" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D81" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E81" t="n">
         <v>0</v>
@@ -3037,16 +3037,16 @@
         <v>44834</v>
       </c>
       <c r="B82" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C82" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D82" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E82" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -3072,10 +3072,10 @@
         <v>50</v>
       </c>
       <c r="C83" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D83" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E83" t="n">
         <v>0</v>
@@ -3093,7 +3093,7 @@
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="84">
@@ -3107,7 +3107,7 @@
         <v>24</v>
       </c>
       <c r="D84" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="E84" t="n">
         <v>0</v>
@@ -3133,16 +3133,16 @@
         <v>44926</v>
       </c>
       <c r="B85" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C85" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D85" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E85" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -3165,16 +3165,16 @@
         <v>44957</v>
       </c>
       <c r="B86" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C86" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D86" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="E86" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -3197,16 +3197,16 @@
         <v>44985</v>
       </c>
       <c r="B87" t="n">
+        <v>38</v>
+      </c>
+      <c r="C87" t="n">
+        <v>20</v>
+      </c>
+      <c r="D87" t="n">
         <v>37</v>
       </c>
-      <c r="C87" t="n">
-        <v>19</v>
-      </c>
-      <c r="D87" t="n">
-        <v>34</v>
-      </c>
       <c r="E87" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -3229,16 +3229,16 @@
         <v>45016</v>
       </c>
       <c r="B88" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C88" t="n">
         <v>20</v>
       </c>
       <c r="D88" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E88" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -3299,10 +3299,10 @@
         <v>17</v>
       </c>
       <c r="D90" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E90" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -3331,10 +3331,10 @@
         <v>18</v>
       </c>
       <c r="D91" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -3357,7 +3357,7 @@
         <v>45138</v>
       </c>
       <c r="B92" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C92" t="n">
         <v>19</v>
@@ -3366,7 +3366,7 @@
         <v>20</v>
       </c>
       <c r="E92" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
@@ -3381,7 +3381,7 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -3389,16 +3389,16 @@
         <v>45169</v>
       </c>
       <c r="B93" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C93" t="n">
         <v>23</v>
       </c>
       <c r="D93" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E93" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F93" t="n">
         <v>0</v>
@@ -3421,16 +3421,16 @@
         <v>45199</v>
       </c>
       <c r="B94" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C94" t="n">
         <v>28</v>
       </c>
       <c r="D94" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E94" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F94" t="n">
         <v>0</v>
@@ -3445,7 +3445,7 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
     </row>
     <row r="95">
@@ -3459,16 +3459,16 @@
         <v>32</v>
       </c>
       <c r="D95" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E95" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F95" t="n">
         <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -3477,7 +3477,7 @@
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
     </row>
     <row r="96">
@@ -3485,16 +3485,16 @@
         <v>45260</v>
       </c>
       <c r="B96" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C96" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D96" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E96" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F96" t="n">
         <v>0</v>
@@ -3506,7 +3506,7 @@
         <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -3517,22 +3517,22 @@
         <v>45291</v>
       </c>
       <c r="B97" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C97" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D97" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E97" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F97" t="n">
         <v>0</v>
       </c>
       <c r="G97" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
@@ -3541,7 +3541,7 @@
         <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -3555,22 +3555,22 @@
         <v>32</v>
       </c>
       <c r="D98" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E98" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F98" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="G98" t="n">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="H98" t="n">
         <v>0</v>
       </c>
       <c r="I98" t="n">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -3584,13 +3584,13 @@
         <v>41</v>
       </c>
       <c r="C99" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D99" t="n">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="E99" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F99" t="n">
         <v>0</v>
@@ -3602,7 +3602,7 @@
         <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -3616,13 +3616,13 @@
         <v>35</v>
       </c>
       <c r="C100" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D100" t="n">
         <v>36</v>
       </c>
       <c r="E100" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F100" t="n">
         <v>0</v>
@@ -3634,7 +3634,7 @@
         <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -3651,10 +3651,10 @@
         <v>27</v>
       </c>
       <c r="D101" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E101" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F101" t="n">
         <v>0</v>
@@ -3666,10 +3666,10 @@
         <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="J101" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
     </row>
     <row r="102">
@@ -3677,16 +3677,16 @@
         <v>45443</v>
       </c>
       <c r="B102" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C102" t="n">
         <v>22</v>
       </c>
       <c r="D102" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E102" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F102" t="n">
         <v>0</v>
@@ -3709,17 +3709,17 @@
         <v>45473</v>
       </c>
       <c r="B103" t="n">
+        <v>29</v>
+      </c>
+      <c r="C103" t="n">
+        <v>29</v>
+      </c>
+      <c r="D103" t="n">
+        <v>31</v>
+      </c>
+      <c r="E103" t="n">
         <v>28</v>
       </c>
-      <c r="C103" t="n">
-        <v>30</v>
-      </c>
-      <c r="D103" t="n">
-        <v>36</v>
-      </c>
-      <c r="E103" t="n">
-        <v>21</v>
-      </c>
       <c r="F103" t="n">
         <v>0</v>
       </c>
@@ -3730,7 +3730,7 @@
         <v>0</v>
       </c>
       <c r="I103" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -3741,22 +3741,22 @@
         <v>45504</v>
       </c>
       <c r="B104" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C104" t="n">
         <v>28</v>
       </c>
       <c r="D104" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E104" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F104" t="n">
         <v>0</v>
       </c>
       <c r="G104" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -3773,16 +3773,16 @@
         <v>45535</v>
       </c>
       <c r="B105" t="n">
+        <v>43</v>
+      </c>
+      <c r="C105" t="n">
+        <v>36</v>
+      </c>
+      <c r="D105" t="n">
         <v>42</v>
       </c>
-      <c r="C105" t="n">
-        <v>34</v>
-      </c>
-      <c r="D105" t="n">
-        <v>55</v>
-      </c>
       <c r="E105" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F105" t="n">
         <v>0</v>
@@ -3797,7 +3797,7 @@
         <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
     </row>
     <row r="106">
@@ -3808,16 +3808,16 @@
         <v>52</v>
       </c>
       <c r="C106" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D106" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E106" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F106" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3826,10 +3826,10 @@
         <v>0</v>
       </c>
       <c r="I106" t="n">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="J106" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="107">
@@ -3840,19 +3840,19 @@
         <v>64</v>
       </c>
       <c r="C107" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D107" t="n">
+        <v>68</v>
+      </c>
+      <c r="E107" t="n">
+        <v>53</v>
+      </c>
+      <c r="F107" t="n">
         <v>72</v>
       </c>
-      <c r="E107" t="n">
-        <v>42</v>
-      </c>
-      <c r="F107" t="n">
-        <v>0</v>
-      </c>
       <c r="G107" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -3861,7 +3861,7 @@
         <v>0</v>
       </c>
       <c r="J107" t="n">
-        <v>56</v>
+        <v>74</v>
       </c>
     </row>
     <row r="108">
@@ -3869,31 +3869,31 @@
         <v>45626</v>
       </c>
       <c r="B108" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C108" t="n">
         <v>64</v>
       </c>
       <c r="D108" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E108" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="F108" t="n">
         <v>0</v>
       </c>
       <c r="G108" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
       </c>
       <c r="I108" t="n">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="J108" t="n">
-        <v>58</v>
+        <v>100</v>
       </c>
     </row>
     <row r="109">
@@ -3901,16 +3901,16 @@
         <v>45657</v>
       </c>
       <c r="B109" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C109" t="n">
         <v>69</v>
       </c>
       <c r="D109" t="n">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="E109" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F109" t="n">
         <v>0</v>
@@ -3922,10 +3922,10 @@
         <v>0</v>
       </c>
       <c r="I109" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="J109" t="n">
-        <v>100</v>
+        <v>62</v>
       </c>
     </row>
     <row r="110">
@@ -3933,22 +3933,22 @@
         <v>45688</v>
       </c>
       <c r="B110" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C110" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D110" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E110" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F110" t="n">
         <v>0</v>
       </c>
       <c r="G110" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -3965,31 +3965,31 @@
         <v>45716</v>
       </c>
       <c r="B111" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C111" t="n">
         <v>56</v>
       </c>
       <c r="D111" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E111" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F111" t="n">
         <v>0</v>
       </c>
       <c r="G111" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
       </c>
       <c r="I111" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="J111" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="112">
@@ -3997,28 +3997,28 @@
         <v>45747</v>
       </c>
       <c r="B112" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C112" t="n">
         <v>56</v>
       </c>
       <c r="D112" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="E112" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F112" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="G112" t="n">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
       </c>
       <c r="I112" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -4029,28 +4029,28 @@
         <v>45777</v>
       </c>
       <c r="B113" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C113" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D113" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E113" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F113" t="n">
         <v>0</v>
       </c>
       <c r="G113" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
       </c>
       <c r="I113" t="n">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -4061,19 +4061,19 @@
         <v>45808</v>
       </c>
       <c r="B114" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C114" t="n">
         <v>38</v>
       </c>
       <c r="D114" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E114" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="F114" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="G114" t="n">
         <v>32</v>
@@ -4082,7 +4082,7 @@
         <v>0</v>
       </c>
       <c r="I114" t="n">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -4099,22 +4099,22 @@
         <v>43</v>
       </c>
       <c r="D115" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E115" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F115" t="n">
         <v>0</v>
       </c>
       <c r="G115" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
       </c>
       <c r="I115" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -4125,22 +4125,22 @@
         <v>45869</v>
       </c>
       <c r="B116" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C116" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D116" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E116" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F116" t="n">
         <v>0</v>
       </c>
       <c r="G116" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
@@ -4157,22 +4157,22 @@
         <v>45900</v>
       </c>
       <c r="B117" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C117" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D117" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="E117" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="F117" t="n">
         <v>0</v>
       </c>
       <c r="G117" t="n">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -4189,22 +4189,22 @@
         <v>45930</v>
       </c>
       <c r="B118" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C118" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D118" t="n">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="E118" t="n">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="F118" t="n">
         <v>0</v>
       </c>
       <c r="G118" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
@@ -4213,7 +4213,7 @@
         <v>0</v>
       </c>
       <c r="J118" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
     </row>
     <row r="119">
@@ -4221,28 +4221,28 @@
         <v>45961</v>
       </c>
       <c r="B119" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C119" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D119" t="n">
         <v>100</v>
       </c>
       <c r="E119" t="n">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="F119" t="n">
         <v>100</v>
       </c>
       <c r="G119" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
       </c>
       <c r="I119" t="n">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -4259,13 +4259,13 @@
         <v>100</v>
       </c>
       <c r="D120" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E120" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F120" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="G120" t="n">
         <v>100</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="I120" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="J120" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="121">
@@ -4285,22 +4285,22 @@
         <v>46022</v>
       </c>
       <c r="B121" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C121" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D121" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E121" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F121" t="n">
         <v>0</v>
       </c>
       <c r="G121" t="n">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -4317,28 +4317,28 @@
         <v>46053</v>
       </c>
       <c r="B122" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C122" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D122" t="n">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="E122" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F122" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="G122" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
       </c>
       <c r="I122" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -4349,28 +4349,28 @@
         <v>46081</v>
       </c>
       <c r="B123" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C123" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D123" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E123" t="n">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="F123" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="G123" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
       </c>
       <c r="I123" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -4381,31 +4381,95 @@
         <v>46112</v>
       </c>
       <c r="B124" t="n">
+        <v>54</v>
+      </c>
+      <c r="C124" t="n">
+        <v>70</v>
+      </c>
+      <c r="D124" t="n">
+        <v>53</v>
+      </c>
+      <c r="E124" t="n">
+        <v>100</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0</v>
+      </c>
+      <c r="G124" t="n">
+        <v>77</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" t="n">
+        <v>53</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B125" t="n">
+        <v>57</v>
+      </c>
+      <c r="C125" t="n">
+        <v>61</v>
+      </c>
+      <c r="D125" t="n">
+        <v>53</v>
+      </c>
+      <c r="E125" t="n">
+        <v>96</v>
+      </c>
+      <c r="F125" t="n">
+        <v>86</v>
+      </c>
+      <c r="G125" t="n">
+        <v>85</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" t="n">
+        <v>61</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B126" t="n">
+        <v>48</v>
+      </c>
+      <c r="C126" t="n">
         <v>56</v>
       </c>
-      <c r="C124" t="n">
-        <v>72</v>
-      </c>
-      <c r="D124" t="n">
-        <v>33</v>
-      </c>
-      <c r="E124" t="n">
-        <v>84</v>
-      </c>
-      <c r="F124" t="n">
-        <v>25</v>
-      </c>
-      <c r="G124" t="n">
-        <v>30</v>
-      </c>
-      <c r="H124" t="n">
-        <v>100</v>
-      </c>
-      <c r="I124" t="n">
-        <v>26</v>
-      </c>
-      <c r="J124" t="n">
-        <v>11</v>
+      <c r="D126" t="n">
+        <v>37</v>
+      </c>
+      <c r="E126" t="n">
+        <v>74</v>
+      </c>
+      <c r="F126" t="n">
+        <v>27</v>
+      </c>
+      <c r="G126" t="n">
+        <v>67</v>
+      </c>
+      <c r="H126" t="n">
+        <v>14</v>
+      </c>
+      <c r="I126" t="n">
+        <v>32</v>
+      </c>
+      <c r="J126" t="n">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/data/plejd_trends_monthly.xlsx
+++ b/data/plejd_trends_monthly.xlsx
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -417,67 +429,67 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J126"/>
+  <dimension ref="A1:J130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Plejd_SE</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Plejd_NO</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Plejd_FI</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Plejd_NL</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Plejd_ES</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Plejd_DE</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Plejd_CH</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Plejd_IS</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Plejd_DK</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -505,7 +517,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B3" t="n">
@@ -537,7 +549,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B4" t="n">
@@ -569,7 +581,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B5" t="n">
@@ -601,7 +613,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B6" t="n">
@@ -633,7 +645,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B7" t="n">
@@ -665,7 +677,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B8" t="n">
@@ -697,11 +709,11 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -729,7 +741,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B10" t="n">
@@ -761,7 +773,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B11" t="n">
@@ -793,7 +805,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B12" t="n">
@@ -825,7 +837,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B13" t="n">
@@ -857,7 +869,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B14" t="n">
@@ -889,7 +901,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B15" t="n">
@@ -921,7 +933,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B16" t="n">
@@ -931,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -953,11 +965,11 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -985,7 +997,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B18" t="n">
@@ -1017,7 +1029,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B19" t="n">
@@ -1049,7 +1061,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B20" t="n">
@@ -1074,14 +1086,14 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B21" t="n">
@@ -1113,7 +1125,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B22" t="n">
@@ -1145,7 +1157,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B23" t="n">
@@ -1177,7 +1189,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B24" t="n">
@@ -1209,7 +1221,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B25" t="n">
@@ -1241,7 +1253,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B26" t="n">
@@ -1273,11 +1285,11 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -1305,7 +1317,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B28" t="n">
@@ -1337,11 +1349,11 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -1369,7 +1381,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B30" t="n">
@@ -1401,7 +1413,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B31" t="n">
@@ -1433,7 +1445,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B32" t="n">
@@ -1465,7 +1477,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B33" t="n">
@@ -1497,7 +1509,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B34" t="n">
@@ -1529,44 +1541,44 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B35" t="n">
+        <v>20</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>43434</v>
+      </c>
+      <c r="B36" t="n">
         <v>21</v>
       </c>
-      <c r="C35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="n">
-        <v>43434</v>
-      </c>
-      <c r="B36" t="n">
-        <v>20</v>
-      </c>
       <c r="C36" t="n">
         <v>0</v>
       </c>
@@ -1593,7 +1605,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B37" t="n">
@@ -1606,7 +1618,7 @@
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -1625,7 +1637,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B38" t="n">
@@ -1657,7 +1669,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B39" t="n">
@@ -1673,7 +1685,7 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1689,11 +1701,11 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B40" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
@@ -1711,7 +1723,7 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
@@ -1721,7 +1733,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B41" t="n">
@@ -1753,7 +1765,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B42" t="n">
@@ -1785,14 +1797,14 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B43" t="n">
         <v>14</v>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
@@ -1817,7 +1829,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B44" t="n">
@@ -1849,7 +1861,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B45" t="n">
@@ -1881,14 +1893,14 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B46" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
@@ -1913,7 +1925,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B47" t="n">
@@ -1945,7 +1957,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B48" t="n">
@@ -1977,7 +1989,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B49" t="n">
@@ -2009,17 +2021,17 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B50" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C50" t="n">
         <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
@@ -2041,7 +2053,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B51" t="n">
@@ -2069,11 +2081,11 @@
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B52" t="n">
@@ -2105,14 +2117,14 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B53" t="n">
         <v>22</v>
       </c>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D53" t="n">
         <v>0</v>
@@ -2137,7 +2149,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B54" t="n">
@@ -2150,7 +2162,7 @@
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -2169,11 +2181,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B55" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C55" t="n">
         <v>0</v>
@@ -2201,7 +2213,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B56" t="n">
@@ -2233,7 +2245,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B57" t="n">
@@ -2265,17 +2277,17 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B58" t="n">
         <v>31</v>
       </c>
       <c r="C58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D58" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
@@ -2297,7 +2309,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B59" t="n">
@@ -2307,7 +2319,7 @@
         <v>4</v>
       </c>
       <c r="D59" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E59" t="n">
         <v>0</v>
@@ -2325,11 +2337,11 @@
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B60" t="n">
@@ -2348,7 +2360,7 @@
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -2361,7 +2373,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B61" t="n">
@@ -2371,7 +2383,7 @@
         <v>6</v>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E61" t="n">
         <v>0</v>
@@ -2393,7 +2405,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B62" t="n">
@@ -2403,7 +2415,7 @@
         <v>6</v>
       </c>
       <c r="D62" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E62" t="n">
         <v>0</v>
@@ -2425,17 +2437,17 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B63" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C63" t="n">
         <v>8</v>
       </c>
       <c r="D63" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
@@ -2457,7 +2469,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B64" t="n">
@@ -2489,17 +2501,17 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B65" t="n">
         <v>32</v>
       </c>
       <c r="C65" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D65" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E65" t="n">
         <v>0</v>
@@ -2521,7 +2533,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B66" t="n">
@@ -2553,14 +2565,14 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B67" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C67" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D67" t="n">
         <v>0</v>
@@ -2585,14 +2597,14 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B68" t="n">
         <v>28</v>
       </c>
       <c r="C68" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D68" t="n">
         <v>0</v>
@@ -2617,7 +2629,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B69" t="n">
@@ -2649,17 +2661,17 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B70" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C70" t="n">
         <v>8</v>
       </c>
       <c r="D70" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E70" t="n">
         <v>0</v>
@@ -2681,7 +2693,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B71" t="n">
@@ -2713,7 +2725,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B72" t="n">
@@ -2723,7 +2735,7 @@
         <v>11</v>
       </c>
       <c r="D72" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E72" t="n">
         <v>0</v>
@@ -2745,14 +2757,14 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B73" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C73" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D73" t="n">
         <v>0</v>
@@ -2777,17 +2789,17 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B74" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C74" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D74" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E74" t="n">
         <v>0</v>
@@ -2809,7 +2821,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B75" t="n">
@@ -2841,46 +2853,46 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B76" t="n">
         <v>30</v>
       </c>
       <c r="C76" t="n">
+        <v>11</v>
+      </c>
+      <c r="D76" t="n">
+        <v>18</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>44681</v>
+      </c>
+      <c r="B77" t="n">
+        <v>31</v>
+      </c>
+      <c r="C77" t="n">
         <v>12</v>
-      </c>
-      <c r="D76" t="n">
-        <v>21</v>
-      </c>
-      <c r="E76" t="n">
-        <v>0</v>
-      </c>
-      <c r="F76" t="n">
-        <v>0</v>
-      </c>
-      <c r="G76" t="n">
-        <v>0</v>
-      </c>
-      <c r="H76" t="n">
-        <v>0</v>
-      </c>
-      <c r="I76" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="1" t="n">
-        <v>44681</v>
-      </c>
-      <c r="B77" t="n">
-        <v>30</v>
-      </c>
-      <c r="C77" t="n">
-        <v>11</v>
       </c>
       <c r="D77" t="n">
         <v>12</v>
@@ -2905,7 +2917,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B78" t="n">
@@ -2915,7 +2927,7 @@
         <v>10</v>
       </c>
       <c r="D78" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E78" t="n">
         <v>0</v>
@@ -2937,7 +2949,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B79" t="n">
@@ -2947,7 +2959,7 @@
         <v>10</v>
       </c>
       <c r="D79" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E79" t="n">
         <v>0</v>
@@ -2969,17 +2981,17 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B80" t="n">
         <v>25</v>
       </c>
       <c r="C80" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D80" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E80" t="n">
         <v>0</v>
@@ -3001,7 +3013,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B81" t="n">
@@ -3011,7 +3023,7 @@
         <v>17</v>
       </c>
       <c r="D81" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E81" t="n">
         <v>0</v>
@@ -3033,7 +3045,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B82" t="n">
@@ -3043,10 +3055,10 @@
         <v>15</v>
       </c>
       <c r="D82" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E82" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -3065,7 +3077,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B83" t="n">
@@ -3075,7 +3087,7 @@
         <v>20</v>
       </c>
       <c r="D83" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E83" t="n">
         <v>0</v>
@@ -3093,21 +3105,21 @@
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B84" t="n">
         <v>55</v>
       </c>
       <c r="C84" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D84" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E84" t="n">
         <v>0</v>
@@ -3125,11 +3137,11 @@
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B85" t="n">
@@ -3142,7 +3154,7 @@
         <v>35</v>
       </c>
       <c r="E85" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -3161,26 +3173,26 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B86" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C86" t="n">
         <v>19</v>
       </c>
       <c r="D86" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E86" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -3193,20 +3205,20 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B87" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C87" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D87" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E87" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -3225,20 +3237,20 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B88" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C88" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D88" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E88" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -3257,20 +3269,20 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B89" t="n">
         <v>28</v>
       </c>
       <c r="C89" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D89" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E89" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
@@ -3289,7 +3301,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B90" t="n">
@@ -3299,10 +3311,10 @@
         <v>17</v>
       </c>
       <c r="D90" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E90" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -3321,7 +3333,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B91" t="n">
@@ -3331,7 +3343,7 @@
         <v>18</v>
       </c>
       <c r="D91" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E91" t="n">
         <v>0</v>
@@ -3343,7 +3355,7 @@
         <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I91" t="n">
         <v>0</v>
@@ -3353,7 +3365,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B92" t="n">
@@ -3363,10 +3375,10 @@
         <v>19</v>
       </c>
       <c r="D92" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E92" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
@@ -3385,17 +3397,17 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B93" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C93" t="n">
         <v>23</v>
       </c>
       <c r="D93" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E93" t="n">
         <v>20</v>
@@ -3417,7 +3429,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B94" t="n">
@@ -3430,7 +3442,7 @@
         <v>40</v>
       </c>
       <c r="E94" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F94" t="n">
         <v>0</v>
@@ -3445,30 +3457,30 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B95" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C95" t="n">
         <v>32</v>
       </c>
       <c r="D95" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E95" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F95" t="n">
         <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -3477,11 +3489,11 @@
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B96" t="n">
@@ -3491,10 +3503,10 @@
         <v>44</v>
       </c>
       <c r="D96" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E96" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F96" t="n">
         <v>0</v>
@@ -3506,14 +3518,14 @@
         <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B97" t="n">
@@ -3523,16 +3535,16 @@
         <v>33</v>
       </c>
       <c r="D97" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E97" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F97" t="n">
         <v>0</v>
       </c>
       <c r="G97" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
@@ -3541,56 +3553,56 @@
         <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B98" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C98" t="n">
         <v>32</v>
       </c>
       <c r="D98" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="E98" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F98" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="G98" t="n">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="H98" t="n">
         <v>0</v>
       </c>
       <c r="I98" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B99" t="n">
         <v>41</v>
       </c>
       <c r="C99" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D99" t="n">
         <v>42</v>
       </c>
       <c r="E99" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F99" t="n">
         <v>0</v>
@@ -3602,27 +3614,27 @@
         <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B100" t="n">
         <v>35</v>
       </c>
       <c r="C100" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D100" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E100" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F100" t="n">
         <v>0</v>
@@ -3634,14 +3646,14 @@
         <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B101" t="n">
@@ -3651,10 +3663,10 @@
         <v>27</v>
       </c>
       <c r="D101" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E101" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F101" t="n">
         <v>0</v>
@@ -3669,11 +3681,11 @@
         <v>57</v>
       </c>
       <c r="J101" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B102" t="n">
@@ -3683,10 +3695,10 @@
         <v>22</v>
       </c>
       <c r="D102" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E102" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F102" t="n">
         <v>0</v>
@@ -3701,24 +3713,24 @@
         <v>0</v>
       </c>
       <c r="J102" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B103" t="n">
         <v>29</v>
       </c>
       <c r="C103" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D103" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E103" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F103" t="n">
         <v>0</v>
@@ -3730,14 +3742,14 @@
         <v>0</v>
       </c>
       <c r="I103" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B104" t="n">
@@ -3747,16 +3759,16 @@
         <v>28</v>
       </c>
       <c r="D104" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E104" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="F104" t="n">
         <v>0</v>
       </c>
       <c r="G104" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -3769,20 +3781,20 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B105" t="n">
         <v>43</v>
       </c>
       <c r="C105" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D105" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E105" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F105" t="n">
         <v>0</v>
@@ -3797,11 +3809,11 @@
         <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B106" t="n">
@@ -3811,13 +3823,13 @@
         <v>47</v>
       </c>
       <c r="D106" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E106" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F106" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3826,33 +3838,33 @@
         <v>0</v>
       </c>
       <c r="I106" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="J106" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B107" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C107" t="n">
+        <v>50</v>
+      </c>
+      <c r="D107" t="n">
         <v>51</v>
       </c>
-      <c r="D107" t="n">
-        <v>68</v>
-      </c>
       <c r="E107" t="n">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="F107" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="G107" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -3861,56 +3873,56 @@
         <v>0</v>
       </c>
       <c r="J107" t="n">
-        <v>74</v>
+        <v>100</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B108" t="n">
         <v>74</v>
       </c>
       <c r="C108" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D108" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E108" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="F108" t="n">
         <v>0</v>
       </c>
       <c r="G108" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
       </c>
       <c r="I108" t="n">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="J108" t="n">
-        <v>100</v>
+        <v>77</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B109" t="n">
         <v>70</v>
       </c>
       <c r="C109" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D109" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E109" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F109" t="n">
         <v>0</v>
@@ -3922,33 +3934,33 @@
         <v>0</v>
       </c>
       <c r="I109" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="J109" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B110" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C110" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D110" t="n">
+        <v>53</v>
+      </c>
+      <c r="E110" t="n">
         <v>56</v>
       </c>
-      <c r="E110" t="n">
-        <v>60</v>
-      </c>
       <c r="F110" t="n">
         <v>0</v>
       </c>
       <c r="G110" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -3961,7 +3973,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B111" t="n">
@@ -3971,61 +3983,61 @@
         <v>56</v>
       </c>
       <c r="D111" t="n">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="E111" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F111" t="n">
         <v>0</v>
       </c>
       <c r="G111" t="n">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
       </c>
       <c r="I111" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="J111" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B112" t="n">
         <v>44</v>
       </c>
       <c r="C112" t="n">
+        <v>55</v>
+      </c>
+      <c r="D112" t="n">
         <v>56</v>
       </c>
-      <c r="D112" t="n">
-        <v>51</v>
-      </c>
       <c r="E112" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F112" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="G112" t="n">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
       </c>
       <c r="I112" t="n">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B113" t="n">
@@ -4035,112 +4047,112 @@
         <v>43</v>
       </c>
       <c r="D113" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E113" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F113" t="n">
         <v>0</v>
       </c>
       <c r="G113" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
       </c>
       <c r="I113" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B114" t="n">
         <v>43</v>
       </c>
       <c r="C114" t="n">
+        <v>37</v>
+      </c>
+      <c r="D114" t="n">
+        <v>42</v>
+      </c>
+      <c r="E114" t="n">
+        <v>44</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" t="n">
         <v>38</v>
       </c>
-      <c r="D114" t="n">
+      <c r="H114" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" t="n">
+        <v>64</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>45838</v>
+      </c>
+      <c r="B115" t="n">
+        <v>40</v>
+      </c>
+      <c r="C115" t="n">
+        <v>42</v>
+      </c>
+      <c r="D115" t="n">
+        <v>39</v>
+      </c>
+      <c r="E115" t="n">
         <v>44</v>
       </c>
-      <c r="E114" t="n">
-        <v>40</v>
-      </c>
-      <c r="F114" t="n">
-        <v>0</v>
-      </c>
-      <c r="G114" t="n">
-        <v>32</v>
-      </c>
-      <c r="H114" t="n">
-        <v>0</v>
-      </c>
-      <c r="I114" t="n">
-        <v>71</v>
-      </c>
-      <c r="J114" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="1" t="n">
-        <v>45838</v>
-      </c>
-      <c r="B115" t="n">
+      <c r="F115" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" t="n">
+        <v>43</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" t="n">
+        <v>70</v>
+      </c>
+      <c r="J115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>45869</v>
+      </c>
+      <c r="B116" t="n">
+        <v>54</v>
+      </c>
+      <c r="C116" t="n">
         <v>39</v>
       </c>
-      <c r="C115" t="n">
-        <v>43</v>
-      </c>
-      <c r="D115" t="n">
-        <v>35</v>
-      </c>
-      <c r="E115" t="n">
-        <v>41</v>
-      </c>
-      <c r="F115" t="n">
-        <v>0</v>
-      </c>
-      <c r="G115" t="n">
-        <v>0</v>
-      </c>
-      <c r="H115" t="n">
-        <v>0</v>
-      </c>
-      <c r="I115" t="n">
-        <v>0</v>
-      </c>
-      <c r="J115" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="1" t="n">
-        <v>45869</v>
-      </c>
-      <c r="B116" t="n">
-        <v>53</v>
-      </c>
-      <c r="C116" t="n">
-        <v>40</v>
-      </c>
       <c r="D116" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E116" t="n">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="F116" t="n">
         <v>0</v>
       </c>
       <c r="G116" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
@@ -4153,26 +4165,26 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B117" t="n">
+        <v>62</v>
+      </c>
+      <c r="C117" t="n">
+        <v>56</v>
+      </c>
+      <c r="D117" t="n">
         <v>61</v>
       </c>
-      <c r="C117" t="n">
-        <v>57</v>
-      </c>
-      <c r="D117" t="n">
-        <v>57</v>
-      </c>
       <c r="E117" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F117" t="n">
         <v>0</v>
       </c>
       <c r="G117" t="n">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -4185,26 +4197,26 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B118" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C118" t="n">
+        <v>66</v>
+      </c>
+      <c r="D118" t="n">
+        <v>83</v>
+      </c>
+      <c r="E118" t="n">
         <v>67</v>
       </c>
-      <c r="D118" t="n">
-        <v>74</v>
-      </c>
-      <c r="E118" t="n">
-        <v>75</v>
-      </c>
       <c r="F118" t="n">
         <v>0</v>
       </c>
       <c r="G118" t="n">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
@@ -4213,43 +4225,43 @@
         <v>0</v>
       </c>
       <c r="J118" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B119" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C119" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D119" t="n">
         <v>100</v>
       </c>
       <c r="E119" t="n">
+        <v>65</v>
+      </c>
+      <c r="F119" t="n">
+        <v>97</v>
+      </c>
+      <c r="G119" t="n">
+        <v>49</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" t="n">
         <v>75</v>
       </c>
-      <c r="F119" t="n">
-        <v>100</v>
-      </c>
-      <c r="G119" t="n">
-        <v>60</v>
-      </c>
-      <c r="H119" t="n">
-        <v>0</v>
-      </c>
-      <c r="I119" t="n">
-        <v>93</v>
-      </c>
       <c r="J119" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B120" t="n">
@@ -4262,214 +4274,342 @@
         <v>99</v>
       </c>
       <c r="E120" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="F120" t="n">
         <v>0</v>
       </c>
       <c r="G120" t="n">
+        <v>98</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" t="n">
+        <v>69</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B121" t="n">
+        <v>85</v>
+      </c>
+      <c r="C121" t="n">
+        <v>88</v>
+      </c>
+      <c r="D121" t="n">
+        <v>75</v>
+      </c>
+      <c r="E121" t="n">
+        <v>90</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" t="n">
+        <v>63</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" t="n">
+        <v>89</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B122" t="n">
+        <v>71</v>
+      </c>
+      <c r="C122" t="n">
+        <v>79</v>
+      </c>
+      <c r="D122" t="n">
+        <v>88</v>
+      </c>
+      <c r="E122" t="n">
+        <v>73</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" t="n">
+        <v>56</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" t="n">
         <v>100</v>
       </c>
-      <c r="H120" t="n">
-        <v>0</v>
-      </c>
-      <c r="I120" t="n">
-        <v>59</v>
-      </c>
-      <c r="J120" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="1" t="n">
-        <v>46022</v>
-      </c>
-      <c r="B121" t="n">
-        <v>87</v>
-      </c>
-      <c r="C121" t="n">
-        <v>90</v>
-      </c>
-      <c r="D121" t="n">
-        <v>73</v>
-      </c>
-      <c r="E121" t="n">
-        <v>99</v>
-      </c>
-      <c r="F121" t="n">
-        <v>0</v>
-      </c>
-      <c r="G121" t="n">
-        <v>72</v>
-      </c>
-      <c r="H121" t="n">
-        <v>0</v>
-      </c>
-      <c r="I121" t="n">
-        <v>100</v>
-      </c>
-      <c r="J121" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="1" t="n">
-        <v>46053</v>
-      </c>
-      <c r="B122" t="n">
-        <v>70</v>
-      </c>
-      <c r="C122" t="n">
-        <v>80</v>
-      </c>
-      <c r="D122" t="n">
-        <v>90</v>
-      </c>
-      <c r="E122" t="n">
-        <v>80</v>
-      </c>
-      <c r="F122" t="n">
-        <v>95</v>
-      </c>
-      <c r="G122" t="n">
-        <v>62</v>
-      </c>
-      <c r="H122" t="n">
-        <v>0</v>
-      </c>
-      <c r="I122" t="n">
-        <v>98</v>
-      </c>
       <c r="J122" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B123" t="n">
         <v>59</v>
       </c>
       <c r="C123" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D123" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E123" t="n">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="F123" t="n">
         <v>0</v>
       </c>
       <c r="G123" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
       </c>
       <c r="I123" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B124" t="n">
         <v>54</v>
       </c>
       <c r="C124" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D124" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E124" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F124" t="n">
         <v>0</v>
       </c>
       <c r="G124" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
       </c>
       <c r="I124" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B125" t="n">
         <v>57</v>
       </c>
       <c r="C125" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D125" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="E125" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="F125" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G125" t="n">
+        <v>79</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B126" t="n">
+        <v>43</v>
+      </c>
+      <c r="C126" t="n">
+        <v>49</v>
+      </c>
+      <c r="D126" t="n">
+        <v>50</v>
+      </c>
+      <c r="E126" t="n">
         <v>85</v>
       </c>
-      <c r="H125" t="n">
-        <v>0</v>
-      </c>
-      <c r="I125" t="n">
-        <v>61</v>
-      </c>
-      <c r="J125" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="1" t="n">
-        <v>46173</v>
-      </c>
-      <c r="B126" t="n">
-        <v>48</v>
-      </c>
-      <c r="C126" t="n">
+      <c r="F126" t="n">
+        <v>94</v>
+      </c>
+      <c r="G126" t="n">
+        <v>65</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B127" t="n">
+        <v>41</v>
+      </c>
+      <c r="C127" t="n">
+        <v>51</v>
+      </c>
+      <c r="D127" t="n">
+        <v>46</v>
+      </c>
+      <c r="E127" t="n">
+        <v>95</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0</v>
+      </c>
+      <c r="G127" t="n">
+        <v>81</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" t="n">
         <v>56</v>
       </c>
-      <c r="D126" t="n">
-        <v>37</v>
-      </c>
-      <c r="E126" t="n">
-        <v>74</v>
-      </c>
-      <c r="F126" t="n">
-        <v>27</v>
-      </c>
-      <c r="G126" t="n">
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B128" t="n">
+        <v>45</v>
+      </c>
+      <c r="C128" t="n">
+        <v>51</v>
+      </c>
+      <c r="D128" t="n">
+        <v>49</v>
+      </c>
+      <c r="E128" t="n">
+        <v>100</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0</v>
+      </c>
+      <c r="G128" t="n">
+        <v>100</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B129" t="n">
+        <v>60</v>
+      </c>
+      <c r="C129" t="n">
+        <v>71</v>
+      </c>
+      <c r="D129" t="n">
+        <v>59</v>
+      </c>
+      <c r="E129" t="n">
+        <v>71</v>
+      </c>
+      <c r="F129" t="n">
+        <v>13</v>
+      </c>
+      <c r="G129" t="n">
+        <v>50</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0</v>
+      </c>
+      <c r="I129" t="n">
+        <v>18</v>
+      </c>
+      <c r="J129" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B130" t="n">
         <v>67</v>
       </c>
-      <c r="H126" t="n">
-        <v>14</v>
-      </c>
-      <c r="I126" t="n">
-        <v>32</v>
-      </c>
-      <c r="J126" t="n">
-        <v>14</v>
+      <c r="C130" t="n">
+        <v>81</v>
+      </c>
+      <c r="D130" t="n">
+        <v>81</v>
+      </c>
+      <c r="E130" t="n">
+        <v>84</v>
+      </c>
+      <c r="F130" t="n">
+        <v>47</v>
+      </c>
+      <c r="G130" t="n">
+        <v>60</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0</v>
+      </c>
+      <c r="I130" t="n">
+        <v>42</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
